--- a/data/citizen_activity_facility/data.xlsx
+++ b/data/citizen_activity_facility/data.xlsx
@@ -507,10 +507,10 @@
         <v>09:00</v>
       </c>
       <c r="K3" t="str">
-        <v>21:00</v>
+        <v>17:00</v>
       </c>
       <c r="L3" t="str">
-        <v>土日祝日は開館（09:00～17:00）。火曜日は休館、ただし、火曜日が祝日の場合は開館で、翌日が休館。年末年始（12/29～1/3）は休館。</v>
+        <v>祝日は開館。火曜日は休館、ただし、火曜日が祝日の場合は開館で、翌日が休館。年末年始（12/29～1/3）は休館。</v>
       </c>
     </row>
     <row r="4">
